--- a/xy10102/output/qc_summary.xlsx
+++ b/xy10102/output/qc_summary.xlsx
@@ -34,7 +34,7 @@
     <t>有效率</t>
   </si>
   <si>
-    <t>82.22%</t>
+    <t>80.45%</t>
   </si>
 </sst>
 </file>
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>3634</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>786</v>
+        <v>864</v>
       </c>
     </row>
     <row r="5" spans="1:2">
